--- a/artfynd/A 13305-2022 artfynd.xlsx
+++ b/artfynd/A 13305-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13305-2022 artfynd.xlsx
+++ b/artfynd/A 13305-2022 artfynd.xlsx
@@ -675,50 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103995831</v>
+        <v>103995836</v>
       </c>
       <c r="B2" t="n">
-        <v>94440</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1841</v>
+        <v>990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Uggleborgsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550808.9178847569</v>
+        <v>550811</v>
       </c>
       <c r="R2" t="n">
-        <v>7018123.77775498</v>
+        <v>7018123</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:56</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Växer på lågans övre del</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103995925</v>
+        <v>103995877</v>
       </c>
       <c r="B3" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550906.0753684066</v>
+        <v>551168</v>
       </c>
       <c r="R3" t="n">
-        <v>7017963.766089346</v>
+        <v>7017871</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:32</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,37 +917,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103995913</v>
+        <v>103995831</v>
       </c>
       <c r="B4" t="n">
-        <v>96251</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>1841</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550976.5525310378</v>
+        <v>550809</v>
       </c>
       <c r="R4" t="n">
-        <v>7017923.931469418</v>
+        <v>7018124</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,15 +1033,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103995936</v>
+        <v>103995925</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550906.0753684066</v>
+        <v>550906</v>
       </c>
       <c r="R5" t="n">
-        <v>7017963.766089346</v>
+        <v>7017964</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1159,15 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103995981</v>
+        <v>103995822</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,21 +1160,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1199,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550810.1528672818</v>
+        <v>551092</v>
       </c>
       <c r="R6" t="n">
-        <v>7018102.648008098</v>
+        <v>7017837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,15 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103995860</v>
+        <v>103995853</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1296,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1300,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550813.2920547992</v>
+        <v>551154</v>
       </c>
       <c r="R7" t="n">
-        <v>7018103.597571266</v>
+        <v>7017813</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1355,7 +1335,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1365,7 +1345,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:53</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,54 +1381,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103995836</v>
+        <v>103995916</v>
       </c>
       <c r="B8" t="n">
-        <v>94437</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>990</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Liten hornflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lophozia ascendens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Warnst.) R.M.Schust.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Uggleborgsberget, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550810.7340305493</v>
+        <v>551169</v>
       </c>
       <c r="R8" t="n">
-        <v>7018122.906479569</v>
+        <v>7017869</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:56</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1490,12 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Växer på lågans övre del</t>
+          <t>08:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1504,7 +1470,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1535,12 +1500,7 @@
         <v>103995939</v>
       </c>
       <c r="B9" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1572,10 +1532,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550942.0231789212</v>
+        <v>550942</v>
       </c>
       <c r="R9" t="n">
-        <v>7017970.1852745</v>
+        <v>7017970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1653,37 +1613,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103995916</v>
+        <v>103995902</v>
       </c>
       <c r="B10" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1693,10 +1648,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>551168.9357510391</v>
+        <v>551103</v>
       </c>
       <c r="R10" t="n">
-        <v>7017869.384043962</v>
+        <v>7017802</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1728,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1738,7 +1693,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,6 +1704,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -1774,15 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103995909</v>
+        <v>103995928</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,21 +1745,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1814,10 +1769,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550987.5573465847</v>
+        <v>551010</v>
       </c>
       <c r="R11" t="n">
-        <v>7017911.955559576</v>
+        <v>7017869</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1849,7 +1804,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1859,7 +1814,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,11 +1825,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Sälg</t>
-        </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -1900,37 +1850,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103995853</v>
+        <v>103995849</v>
       </c>
       <c r="B12" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1940,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>551153.6113939462</v>
+        <v>551124</v>
       </c>
       <c r="R12" t="n">
-        <v>7017812.887330757</v>
+        <v>7017794</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2021,37 +1966,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103995875</v>
+        <v>103995829</v>
       </c>
       <c r="B13" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219880</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2061,10 +2001,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>551020.2073980058</v>
+        <v>550994</v>
       </c>
       <c r="R13" t="n">
-        <v>7017870.621767861</v>
+        <v>7017917</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2096,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2106,7 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2142,37 +2082,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103995907</v>
+        <v>103995909</v>
       </c>
       <c r="B14" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2182,10 +2117,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>551022.8819641122</v>
+        <v>550988</v>
       </c>
       <c r="R14" t="n">
-        <v>7017872.464266236</v>
+        <v>7017912</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2152,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2227,7 +2162,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2238,6 +2173,11 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -2263,37 +2203,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103995965</v>
+        <v>103995936</v>
       </c>
       <c r="B15" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2303,10 +2238,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550996.4891425283</v>
+        <v>550906</v>
       </c>
       <c r="R15" t="n">
-        <v>7017917.04729247</v>
+        <v>7017964</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,7 +2273,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2348,7 +2283,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:32</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2384,15 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103995829</v>
+        <v>103995981</v>
       </c>
       <c r="B16" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2424,10 +2354,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550993.3355578909</v>
+        <v>550810</v>
       </c>
       <c r="R16" t="n">
-        <v>7017916.99729706</v>
+        <v>7018103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2459,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2469,7 +2399,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2505,37 +2435,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103995928</v>
+        <v>103995907</v>
       </c>
       <c r="B17" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2545,10 +2470,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>551009.8668735665</v>
+        <v>551023</v>
       </c>
       <c r="R17" t="n">
-        <v>7017869.107715114</v>
+        <v>7017873</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2580,7 +2505,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2590,7 +2515,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2626,32 +2551,27 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103995902</v>
+        <v>103995965</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2666,10 +2586,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>551102.8519624122</v>
+        <v>550997</v>
       </c>
       <c r="R18" t="n">
-        <v>7017802.629950421</v>
+        <v>7017917</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2701,7 +2621,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2711,7 +2631,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,11 +2642,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Tall</t>
-        </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -2752,37 +2667,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103995877</v>
+        <v>103995913</v>
       </c>
       <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>219790</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2792,10 +2702,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>551168.0060866199</v>
+        <v>550976</v>
       </c>
       <c r="R19" t="n">
-        <v>7017871.169334965</v>
+        <v>7017924</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2827,7 +2737,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2837,7 +2747,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>08:58</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2873,37 +2783,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103995849</v>
+        <v>103995875</v>
       </c>
       <c r="B20" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>219880</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2913,10 +2818,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>551124.1769460342</v>
+        <v>551020</v>
       </c>
       <c r="R20" t="n">
-        <v>7017793.518174782</v>
+        <v>7017870</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2948,7 +2853,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2958,7 +2863,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2997,12 +2902,7 @@
         <v>103995830</v>
       </c>
       <c r="B21" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3034,10 +2934,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>551125.8503504989</v>
+        <v>551126</v>
       </c>
       <c r="R21" t="n">
-        <v>7017801.645306157</v>
+        <v>7017802</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3118,12 +3018,7 @@
         <v>103995977</v>
       </c>
       <c r="B22" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3155,10 +3050,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550959.354705428</v>
+        <v>550959</v>
       </c>
       <c r="R22" t="n">
-        <v>7017928.609087816</v>
+        <v>7017929</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3236,15 +3131,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103995822</v>
+        <v>103995860</v>
       </c>
       <c r="B23" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3252,21 +3142,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3276,10 +3166,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>551092.3900923097</v>
+        <v>550813</v>
       </c>
       <c r="R23" t="n">
-        <v>7017837.115806463</v>
+        <v>7018104</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3311,7 +3201,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3321,7 +3211,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:53</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 13305-2022 artfynd.xlsx
+++ b/artfynd/A 13305-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995836</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995877</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1030,6 +1045,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,6 +1166,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995925</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995822</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995853</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1610,6 +1650,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995939</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995902</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1847,6 +1897,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995928</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1963,6 +2018,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995849</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2079,6 +2139,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995829</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2200,6 +2265,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995909</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2316,6 +2386,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995936</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2432,6 +2507,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995981</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2548,6 +2628,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995907</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2664,6 +2749,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995965</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2780,6 +2870,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995913</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2896,6 +2991,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995875</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3012,6 +3112,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995830</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3128,6 +3233,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995977</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3244,8 +3354,37 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103995860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>